--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2022.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -11962,7 +11962,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13756,7 +13756,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13986,7 +13986,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14676,7 +14676,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2022.xlsx
@@ -2101,7 +2101,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:48</t>
+    <t xml:space="preserve">2026-09-07 12:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_medianeta_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_medianeta_a_2022.xlsx
@@ -2101,7 +2101,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:53</t>
+    <t xml:space="preserve">2026-09-08 10:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
